--- a/library/Library_Data/Data.xlsx
+++ b/library/Library_Data/Data.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.85546875" customWidth="1" min="1" max="1"/>
@@ -946,6 +946,220 @@
         <v>14</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Wasim Shah</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>8980989098</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>MYTH10001</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>The Palace of Illusions</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Chitra Banerjee Divakaruni</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>14-09-2026</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Wasim Shah</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>8980989098</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>MYTH10004</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>The Pregnant King</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Devdutt Pattanaik</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Wasim Shah</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>8980989098</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>NOV10009</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>The Lowland</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Jhumpa Lahiri</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>399</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>13-09-2026</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Wasim Shah</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>8980989098</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>ROMNC10004</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Can Love Happen Twice?</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Ravinder Singh</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
